--- a/static/data/exports/Retro_TR_GE_2009.xlsx
+++ b/static/data/exports/Retro_TR_GE_2009.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_TR_GE_2009.xlsx
+++ b/static/data/exports/Retro_TR_GE_2009.xlsx
@@ -540,11 +540,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E2" t="n">
         <v>16134</v>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E12" t="n">
         <v>15790</v>
@@ -1780,11 +1780,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E22" t="n">
         <v>17791</v>
@@ -2400,11 +2400,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E32" t="n">
         <v>16103</v>
@@ -3020,11 +3020,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E42" t="n">
         <v>20928</v>
@@ -3640,11 +3640,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E52" t="n">
         <v>17746</v>
@@ -4260,11 +4260,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E62" t="n">
         <v>16348</v>
@@ -4880,11 +4880,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E72" t="n">
         <v>15444</v>
@@ -5500,11 +5500,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E82" t="n">
         <v>13271</v>
@@ -6120,11 +6120,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E92" t="n">
         <v>20941</v>
@@ -6740,11 +6740,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E102" t="n">
         <v>19340</v>
@@ -7360,11 +7360,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E112" t="n">
         <v>16480</v>
@@ -7980,11 +7980,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E122" t="n">
         <v>22524</v>
@@ -8600,11 +8600,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E132" t="n">
         <v>22295</v>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E142" t="n">
         <v>17353</v>
@@ -9840,11 +9840,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E152" t="n">
         <v>19265</v>
@@ -10460,11 +10460,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E162" t="n">
         <v>17094</v>
@@ -11080,11 +11080,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E172" t="n">
         <v>20250</v>
@@ -11700,11 +11700,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E182" t="n">
         <v>15442</v>
@@ -12320,11 +12320,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E192" t="n">
         <v>15702</v>
@@ -12940,11 +12940,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E202" t="n">
         <v>19577</v>
@@ -13560,11 +13560,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E212" t="n">
         <v>16923</v>
@@ -14180,11 +14180,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E222" t="n">
         <v>19522</v>
@@ -14800,11 +14800,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E232" t="n">
         <v>18522</v>
@@ -15358,11 +15358,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E241" t="n">
         <v>22398</v>
@@ -15916,11 +15916,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E250" t="n">
         <v>17013</v>
@@ -16474,11 +16474,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E259" t="n">
         <v>18289</v>
@@ -17032,11 +17032,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E268" t="n">
         <v>16666</v>
@@ -17590,11 +17590,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E277" t="n">
         <v>15080</v>
@@ -18148,11 +18148,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E286" t="n">
         <v>21109</v>
@@ -18768,11 +18768,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E296" t="n">
         <v>18865</v>
@@ -19388,11 +19388,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E306" t="n">
         <v>21860</v>
@@ -20008,11 +20008,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E316" t="n">
         <v>24377</v>
@@ -20628,11 +20628,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E326" t="n">
         <v>22160</v>
@@ -21248,11 +21248,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E336" t="n">
         <v>19442</v>
@@ -21868,11 +21868,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E346" t="n">
         <v>20361</v>
@@ -22488,11 +22488,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E356" t="n">
         <v>23271</v>
@@ -23046,11 +23046,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E365" t="n">
         <v>23467</v>
@@ -23604,11 +23604,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E374" t="n">
         <v>18890</v>
@@ -24162,11 +24162,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E383" t="n">
         <v>20619</v>
@@ -24720,11 +24720,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E392" t="n">
         <v>14478</v>
@@ -25278,11 +25278,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E401" t="n">
         <v>17338</v>
@@ -25836,11 +25836,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E410" t="n">
         <v>14954</v>
@@ -26394,11 +26394,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E419" t="n">
         <v>18014</v>
@@ -26952,11 +26952,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E428" t="n">
         <v>19225</v>
@@ -27510,11 +27510,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E437" t="n">
         <v>19409</v>
@@ -28068,11 +28068,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E446" t="n">
         <v>18599</v>
@@ -28626,11 +28626,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E455" t="n">
         <v>14177</v>
@@ -29184,11 +29184,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E464" t="n">
         <v>14713</v>
@@ -29742,11 +29742,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E473" t="n">
         <v>18274</v>
@@ -30300,11 +30300,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E482" t="n">
         <v>16912</v>
@@ -30858,11 +30858,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E491" t="n">
         <v>17955</v>
@@ -31416,11 +31416,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E500" t="n">
         <v>15167</v>
@@ -31974,11 +31974,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E509" t="n">
         <v>13877</v>
@@ -32532,11 +32532,11 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E518" t="n">
         <v>15089</v>
@@ -33090,11 +33090,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E527" t="n">
         <v>13968</v>
@@ -33648,11 +33648,11 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E536" t="n">
         <v>17364</v>
@@ -34206,11 +34206,11 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E545" t="n">
         <v>14875</v>
@@ -34764,11 +34764,11 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E554" t="n">
         <v>15094</v>
@@ -35322,11 +35322,11 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E563" t="n">
         <v>14493</v>
